--- a/VSXY.xlsx
+++ b/VSXY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867BD0D7-45C2-46CC-BF39-43AEB96C9BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5225CAF4-AEC7-4088-8112-A16EABEFF69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{61D1022A-C31F-435A-9D37-34AD93DFA669}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{61D1022A-C31F-435A-9D37-34AD93DFA669}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>VSCO</t>
   </si>
@@ -142,12 +142,6 @@
   </si>
   <si>
     <t>International</t>
-  </si>
-  <si>
-    <t>Average Store Size in SF</t>
-  </si>
-  <si>
-    <t>Total Selling Square Feet in TSF</t>
   </si>
   <si>
     <t>US Stores</t>
@@ -262,16 +256,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -317,36 +309,39 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -700,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>74.900000000000006</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -710,8 +705,8 @@
       <c r="I3" s="3">
         <v>79.491729000000007</v>
       </c>
-      <c r="J3" s="16" t="s">
-        <v>57</v>
+      <c r="J3" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -723,11 +718,11 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>5953.9305021000009</v>
+        <v>5852.1810889800008</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -736,8 +731,8 @@
       <c r="I5" s="3">
         <v>207</v>
       </c>
-      <c r="J5" s="16" t="s">
-        <v>57</v>
+      <c r="J5" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -748,8 +743,8 @@
         <f>4+986</f>
         <v>990</v>
       </c>
-      <c r="J6" s="16" t="s">
-        <v>57</v>
+      <c r="J6" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -758,27 +753,30 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>6736.9305021000009</v>
+        <v>6635.1810889800008</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{84AFC42E-27B5-4F66-8757-9E4BBB816E4E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D94876DA-AE76-4507-A1D0-03051E2114DC}">
-  <dimension ref="A1:CK419"/>
+  <dimension ref="A1:CK417"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="2" customWidth="1"/>
@@ -817,28 +815,28 @@
         <v>18</v>
       </c>
       <c r="K2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="O2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="R2" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="R2" s="16" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:89" x14ac:dyDescent="0.2">
@@ -848,33 +846,35 @@
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
       <c r="E3" s="9">
-        <v>6833</v>
+        <v>812</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9">
-        <v>6849</v>
+        <v>805</v>
       </c>
       <c r="H3" s="9">
-        <v>6892</v>
+        <v>793</v>
       </c>
       <c r="I3" s="9">
-        <v>6878</v>
+        <v>808</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9">
-        <v>6905</v>
+        <v>772</v>
       </c>
       <c r="L3" s="9">
-        <v>6907</v>
+        <v>763</v>
       </c>
       <c r="M3" s="9">
-        <v>6914</v>
+        <v>782</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9">
-        <v>6913</v>
-      </c>
-      <c r="P3" s="9"/>
+        <v>767</v>
+      </c>
+      <c r="P3" s="9">
+        <v>762</v>
+      </c>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
@@ -956,33 +956,35 @@
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9">
-        <v>5610</v>
+        <v>25</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9">
-        <v>5555</v>
+        <v>23</v>
       </c>
       <c r="H4" s="9">
-        <v>5507</v>
+        <v>23</v>
       </c>
       <c r="I4" s="9">
-        <v>5468</v>
+        <v>23</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9">
-        <v>5365</v>
+        <v>23</v>
       </c>
       <c r="L4" s="9">
-        <v>5305</v>
+        <v>24</v>
       </c>
       <c r="M4" s="9">
-        <v>5337</v>
+        <v>24</v>
       </c>
       <c r="N4" s="9"/>
       <c r="O4" s="9">
-        <v>5323</v>
-      </c>
-      <c r="P4" s="9"/>
+        <v>24</v>
+      </c>
+      <c r="P4" s="9">
+        <v>26</v>
+      </c>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -1064,33 +1066,35 @@
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9">
-        <v>812</v>
+        <v>72</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9">
-        <v>805</v>
+        <v>71</v>
       </c>
       <c r="H5" s="9">
-        <v>793</v>
+        <v>70</v>
       </c>
       <c r="I5" s="9">
-        <v>808</v>
+        <v>70</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9">
-        <v>772</v>
+        <v>68</v>
       </c>
       <c r="L5" s="9">
-        <v>763</v>
+        <v>63</v>
       </c>
       <c r="M5" s="9">
-        <v>782</v>
+        <v>70</v>
       </c>
       <c r="N5" s="9"/>
       <c r="O5" s="9">
-        <v>767</v>
-      </c>
-      <c r="P5" s="9"/>
+        <v>64</v>
+      </c>
+      <c r="P5" s="9">
+        <v>61</v>
+      </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
@@ -1172,33 +1176,35 @@
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9">
-        <v>25</v>
+        <v>443</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9">
-        <v>23</v>
+        <v>473</v>
       </c>
       <c r="H6" s="9">
-        <v>23</v>
+        <v>481</v>
       </c>
       <c r="I6" s="9">
-        <v>23</v>
+        <v>463</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9">
-        <v>23</v>
+        <v>510</v>
       </c>
       <c r="L6" s="9">
-        <v>24</v>
+        <v>521</v>
       </c>
       <c r="M6" s="9">
-        <v>24</v>
+        <v>505</v>
       </c>
       <c r="N6" s="9"/>
       <c r="O6" s="9">
-        <v>24</v>
-      </c>
-      <c r="P6" s="9"/>
+        <v>565</v>
+      </c>
+      <c r="P6" s="9">
+        <v>578</v>
+      </c>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
@@ -1280,33 +1286,35 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="H7" s="9">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="I7" s="9">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="L7" s="9">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="M7" s="9">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="9">
-        <v>64</v>
-      </c>
-      <c r="P7" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="P7" s="9">
+        <v>3</v>
+      </c>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
@@ -1382,39 +1390,65 @@
       <c r="CK7" s="9"/>
     </row>
     <row r="8" spans="1:89" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9">
-        <v>443</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9">
-        <v>473</v>
-      </c>
-      <c r="H8" s="9">
-        <v>481</v>
-      </c>
-      <c r="I8" s="9">
-        <v>463</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9">
-        <v>510</v>
-      </c>
-      <c r="L8" s="9">
-        <v>521</v>
-      </c>
-      <c r="M8" s="9">
-        <v>505</v>
-      </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9">
-        <v>565</v>
-      </c>
-      <c r="P8" s="9"/>
+      <c r="C8" s="10">
+        <f t="shared" ref="C8:H8" si="0">+SUM(C3:C7)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="0"/>
+        <v>1358</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>1378</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="0"/>
+        <v>1373</v>
+      </c>
+      <c r="I8" s="10">
+        <f>+SUM(I3:I7)</f>
+        <v>1370</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" ref="J8:P8" si="1">+SUM(J3:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="1"/>
+        <v>1378</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="1"/>
+        <v>1376</v>
+      </c>
+      <c r="M8" s="10">
+        <f t="shared" si="1"/>
+        <v>1387</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="10">
+        <f t="shared" si="1"/>
+        <v>1423</v>
+      </c>
+      <c r="P8" s="10">
+        <f t="shared" si="1"/>
+        <v>1430</v>
+      </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
@@ -1490,38 +1524,19 @@
       <c r="CK8" s="9"/>
     </row>
     <row r="9" spans="1:89" x14ac:dyDescent="0.2">
-      <c r="B9" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
-      <c r="E9" s="9">
-        <v>6</v>
-      </c>
+      <c r="E9" s="9"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="9">
-        <v>6</v>
-      </c>
-      <c r="H9" s="9">
-        <v>6</v>
-      </c>
-      <c r="I9" s="9">
-        <v>6</v>
-      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="9"/>
-      <c r="K9" s="9">
-        <v>5</v>
-      </c>
-      <c r="L9" s="9">
-        <v>5</v>
-      </c>
-      <c r="M9" s="9">
-        <v>6</v>
-      </c>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="9">
-        <v>3</v>
-      </c>
+      <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
@@ -1598,62 +1613,41 @@
       <c r="CK9" s="9"/>
     </row>
     <row r="10" spans="1:89" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="10">
-        <f t="shared" ref="C10:H10" si="0">+SUM(C5:C9)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="10">
-        <f t="shared" si="0"/>
-        <v>1358</v>
-      </c>
-      <c r="F10" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="10">
-        <f t="shared" si="0"/>
-        <v>1378</v>
-      </c>
-      <c r="H10" s="10">
-        <f t="shared" si="0"/>
-        <v>1373</v>
-      </c>
-      <c r="I10" s="10">
-        <f>+SUM(I5:I9)</f>
-        <v>1370</v>
-      </c>
-      <c r="J10" s="10">
-        <f t="shared" ref="J10:O10" si="1">+SUM(J5:J9)</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="10">
-        <f t="shared" si="1"/>
-        <v>1378</v>
-      </c>
-      <c r="L10" s="10">
-        <f t="shared" si="1"/>
-        <v>1376</v>
-      </c>
-      <c r="M10" s="10">
-        <f t="shared" si="1"/>
-        <v>1387</v>
-      </c>
-      <c r="N10" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="10">
-        <f t="shared" si="1"/>
-        <v>1423</v>
-      </c>
-      <c r="P10" s="9"/>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9">
+        <v>723</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9">
+        <v>729</v>
+      </c>
+      <c r="H10" s="9">
+        <v>800</v>
+      </c>
+      <c r="I10" s="9">
+        <v>738</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9">
+        <v>721</v>
+      </c>
+      <c r="L10" s="9">
+        <v>825</v>
+      </c>
+      <c r="M10" s="9">
+        <v>778</v>
+      </c>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9">
+        <v>803</v>
+      </c>
+      <c r="P10" s="9">
+        <v>897.9</v>
+      </c>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
@@ -1729,20 +1723,41 @@
       <c r="CK10" s="9"/>
     </row>
     <row r="11" spans="1:89" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="E11" s="9">
+        <v>382</v>
+      </c>
       <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="G11" s="9">
+        <v>449</v>
+      </c>
+      <c r="H11" s="9">
+        <v>430</v>
+      </c>
+      <c r="I11" s="9">
+        <v>411</v>
+      </c>
       <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
+      <c r="K11" s="9">
+        <v>433</v>
+      </c>
+      <c r="L11" s="9">
+        <v>406</v>
+      </c>
+      <c r="M11" s="9">
+        <v>429</v>
+      </c>
       <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="O11" s="9">
+        <v>469</v>
+      </c>
+      <c r="P11" s="9">
+        <v>439.4</v>
+      </c>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
@@ -1819,38 +1834,40 @@
     </row>
     <row r="12" spans="1:89" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9">
-        <v>723</v>
+        <v>160</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9">
-        <v>729</v>
+        <v>181</v>
       </c>
       <c r="H12" s="9">
-        <v>800</v>
+        <v>187</v>
       </c>
       <c r="I12" s="9">
-        <v>738</v>
+        <v>198</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9">
-        <v>721</v>
+        <v>199</v>
       </c>
       <c r="L12" s="9">
-        <v>825</v>
+        <v>228</v>
       </c>
       <c r="M12" s="9">
-        <v>778</v>
+        <v>265</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="9">
-        <v>803</v>
-      </c>
-      <c r="P12" s="9"/>
+        <v>288</v>
+      </c>
+      <c r="P12" s="9">
+        <v>273.39999999999998</v>
+      </c>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
@@ -1926,39 +1943,41 @@
       <c r="CK12" s="9"/>
     </row>
     <row r="13" spans="1:89" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9">
-        <v>382</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9">
-        <v>449</v>
-      </c>
-      <c r="H13" s="9">
-        <v>430</v>
-      </c>
-      <c r="I13" s="9">
-        <v>411</v>
-      </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9">
-        <v>433</v>
-      </c>
-      <c r="L13" s="9">
-        <v>406</v>
-      </c>
-      <c r="M13" s="9">
-        <v>429</v>
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10">
+        <v>1265</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10">
+        <v>1359</v>
+      </c>
+      <c r="H13" s="10">
+        <v>1417</v>
+      </c>
+      <c r="I13" s="10">
+        <v>1347</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10">
+        <v>1353</v>
+      </c>
+      <c r="L13" s="10">
+        <v>1459</v>
+      </c>
+      <c r="M13" s="10">
+        <v>1472</v>
       </c>
       <c r="N13" s="9"/>
-      <c r="O13" s="9">
-        <v>469</v>
-      </c>
-      <c r="P13" s="9"/>
+      <c r="O13" s="10">
+        <v>1560</v>
+      </c>
+      <c r="P13" s="10">
+        <v>1610.703</v>
+      </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
@@ -2035,38 +2054,40 @@
     </row>
     <row r="14" spans="1:89" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9">
-        <v>160</v>
+        <v>838</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9">
-        <v>181</v>
+        <v>858</v>
       </c>
       <c r="H14" s="9">
-        <v>187</v>
+        <v>916</v>
       </c>
       <c r="I14" s="9">
-        <v>198</v>
+        <v>879</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9">
-        <v>199</v>
+        <v>879</v>
       </c>
       <c r="L14" s="9">
-        <v>228</v>
+        <v>940</v>
       </c>
       <c r="M14" s="9">
-        <v>265</v>
+        <v>936</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9">
-        <v>288</v>
-      </c>
-      <c r="P14" s="9"/>
+        <v>975</v>
+      </c>
+      <c r="P14" s="9">
+        <v>851.41899999999998</v>
+      </c>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
@@ -2142,39 +2163,65 @@
       <c r="CK14" s="9"/>
     </row>
     <row r="15" spans="1:89" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10">
-        <v>1265</v>
-      </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10">
-        <v>1359</v>
-      </c>
-      <c r="H15" s="10">
-        <v>1417</v>
-      </c>
-      <c r="I15" s="10">
-        <v>1347</v>
-      </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10">
-        <v>1353</v>
-      </c>
-      <c r="L15" s="10">
-        <v>1459</v>
-      </c>
-      <c r="M15" s="10">
-        <v>1472</v>
-      </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="10">
-        <v>1560</v>
-      </c>
-      <c r="P15" s="9"/>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="9">
+        <f t="shared" ref="C15:H15" si="2">+C13-C14</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" si="2"/>
+        <v>427</v>
+      </c>
+      <c r="F15" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <f t="shared" si="2"/>
+        <v>501</v>
+      </c>
+      <c r="H15" s="9">
+        <f t="shared" si="2"/>
+        <v>501</v>
+      </c>
+      <c r="I15" s="9">
+        <f>+I13-I14</f>
+        <v>468</v>
+      </c>
+      <c r="J15" s="9">
+        <f t="shared" ref="J15:P15" si="3">+J13-J14</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="shared" si="3"/>
+        <v>474</v>
+      </c>
+      <c r="L15" s="9">
+        <f t="shared" si="3"/>
+        <v>519</v>
+      </c>
+      <c r="M15" s="9">
+        <f t="shared" si="3"/>
+        <v>536</v>
+      </c>
+      <c r="N15" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
+        <f t="shared" si="3"/>
+        <v>585</v>
+      </c>
+      <c r="P15" s="9">
+        <f t="shared" si="3"/>
+        <v>759.28399999999999</v>
+      </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
@@ -2251,38 +2298,40 @@
     </row>
     <row r="16" spans="1:89" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
-        <v>838</v>
+        <v>494</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9">
-        <v>858</v>
+        <v>475</v>
       </c>
       <c r="H16" s="9">
-        <v>916</v>
+        <v>439</v>
       </c>
       <c r="I16" s="9">
-        <v>879</v>
+        <v>515</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9">
-        <v>879</v>
+        <v>454</v>
       </c>
       <c r="L16" s="9">
-        <v>940</v>
+        <v>478</v>
       </c>
       <c r="M16" s="9">
-        <v>936</v>
+        <v>555</v>
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="9">
-        <v>975</v>
-      </c>
-      <c r="P16" s="9"/>
+        <v>509</v>
+      </c>
+      <c r="P16" s="9">
+        <v>502.654</v>
+      </c>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
@@ -2359,61 +2408,64 @@
     </row>
     <row r="17" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" ref="C17:H17" si="2">+C15-C16</f>
+        <f t="shared" ref="C17:H17" si="4">+C15-C16</f>
         <v>0</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="2"/>
-        <v>427</v>
+        <f t="shared" si="4"/>
+        <v>-67</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="9">
-        <f t="shared" si="2"/>
-        <v>501</v>
+        <f t="shared" si="4"/>
+        <v>26</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" si="2"/>
-        <v>501</v>
+        <f t="shared" si="4"/>
+        <v>62</v>
       </c>
       <c r="I17" s="9">
         <f>+I15-I16</f>
-        <v>468</v>
+        <v>-47</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" ref="J17:O17" si="3">+J15-J16</f>
+        <f t="shared" ref="J17:P17" si="5">+J15-J16</f>
         <v>0</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="3"/>
-        <v>474</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="3"/>
-        <v>519</v>
+        <f t="shared" si="5"/>
+        <v>41</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="3"/>
-        <v>536</v>
+        <f t="shared" si="5"/>
+        <v>-19</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="3"/>
-        <v>585</v>
-      </c>
-      <c r="P17" s="9"/>
+        <f t="shared" si="5"/>
+        <v>76</v>
+      </c>
+      <c r="P17" s="9">
+        <f t="shared" si="5"/>
+        <v>256.63</v>
+      </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
@@ -2490,38 +2542,40 @@
     </row>
     <row r="18" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9">
-        <v>494</v>
+        <v>26</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9">
-        <v>475</v>
+        <v>22</v>
       </c>
       <c r="H18" s="9">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="I18" s="9">
-        <v>515</v>
+        <v>22</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9">
-        <v>454</v>
+        <v>17</v>
       </c>
       <c r="L18" s="9">
-        <v>478</v>
+        <v>18</v>
       </c>
       <c r="M18" s="9">
-        <v>555</v>
+        <v>18</v>
       </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9">
-        <v>509</v>
-      </c>
-      <c r="P18" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="P18" s="9">
+        <v>14.679</v>
+      </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
@@ -2598,61 +2652,40 @@
     </row>
     <row r="19" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="9">
-        <f t="shared" ref="C19:H19" si="4">+C17-C18</f>
+        <v>25</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9">
         <v>0</v>
       </c>
-      <c r="D19" s="9">
-        <f t="shared" si="4"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9">
         <v>0</v>
       </c>
-      <c r="E19" s="9">
-        <f t="shared" si="4"/>
-        <v>-67</v>
-      </c>
-      <c r="F19" s="9">
-        <f t="shared" si="4"/>
+      <c r="I19" s="9">
+        <v>-1</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9">
+        <v>3</v>
+      </c>
+      <c r="L19" s="9">
+        <v>1</v>
+      </c>
+      <c r="M19" s="9">
         <v>0</v>
       </c>
-      <c r="G19" s="9">
-        <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="H19" s="9">
-        <f t="shared" si="4"/>
-        <v>62</v>
-      </c>
-      <c r="I19" s="9">
-        <f>+I17-I18</f>
-        <v>-47</v>
-      </c>
-      <c r="J19" s="9">
-        <f t="shared" ref="J19:O19" si="5">+J17-J18</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="9">
-        <f t="shared" si="5"/>
-        <v>20</v>
-      </c>
-      <c r="L19" s="9">
-        <f t="shared" si="5"/>
-        <v>41</v>
-      </c>
-      <c r="M19" s="9">
-        <f t="shared" si="5"/>
-        <v>-19</v>
-      </c>
-      <c r="N19" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="N19" s="9"/>
       <c r="O19" s="9">
-        <f t="shared" si="5"/>
-        <v>76</v>
-      </c>
-      <c r="P19" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="P19" s="9">
+        <v>5.782</v>
+      </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
@@ -2729,38 +2762,64 @@
     </row>
     <row r="20" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="9">
+        <f t="shared" ref="C20:H20" si="6">+C17-C18+C19</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <f t="shared" si="6"/>
+        <v>-93</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="6"/>
+        <v>41</v>
+      </c>
+      <c r="I20" s="9">
+        <f>+I17-I18+I19</f>
+        <v>-70</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" ref="J20:P20" si="7">+J17-J18+J19</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9">
-        <v>26</v>
-      </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9">
-        <v>22</v>
-      </c>
-      <c r="H20" s="9">
-        <v>21</v>
-      </c>
-      <c r="I20" s="9">
-        <v>22</v>
-      </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9">
-        <v>17</v>
-      </c>
-      <c r="L20" s="9">
-        <v>18</v>
-      </c>
       <c r="M20" s="9">
-        <v>18</v>
-      </c>
-      <c r="N20" s="9"/>
+        <f t="shared" si="7"/>
+        <v>-37</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O20" s="9">
-        <v>15</v>
-      </c>
-      <c r="P20" s="9"/>
+        <f t="shared" si="7"/>
+        <v>64</v>
+      </c>
+      <c r="P20" s="9">
+        <f t="shared" si="7"/>
+        <v>247.733</v>
+      </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
@@ -2837,38 +2896,40 @@
     </row>
     <row r="21" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H21" s="9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I21" s="9">
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9">
         <v>3</v>
       </c>
       <c r="L21" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M21" s="9">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="N21" s="9"/>
       <c r="O21" s="9">
-        <v>3</v>
-      </c>
-      <c r="P21" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="P21" s="9">
+        <v>59.606000000000002</v>
+      </c>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
@@ -2945,61 +3006,64 @@
     </row>
     <row r="22" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:H22" si="6">+C19-C20+C21</f>
+        <f t="shared" ref="C22:H22" si="8">+C20-C21</f>
         <v>0</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="6"/>
-        <v>-93</v>
+        <f t="shared" si="8"/>
+        <v>-71</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>-3</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="6"/>
-        <v>41</v>
+        <f t="shared" si="8"/>
+        <v>32</v>
       </c>
       <c r="I22" s="9">
-        <f>+I19-I20+I21</f>
-        <v>-70</v>
+        <f>+I20-I21</f>
+        <v>-55</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ref="J22:O22" si="7">+J19-J20+J21</f>
+        <f t="shared" ref="J22:P22" si="9">+J20-J21</f>
         <v>0</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="7"/>
-        <v>24</v>
+        <f t="shared" si="9"/>
+        <v>18</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="7"/>
-        <v>-37</v>
+        <f t="shared" si="9"/>
+        <v>-31</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="7"/>
-        <v>64</v>
-      </c>
-      <c r="P22" s="9"/>
+        <f t="shared" si="9"/>
+        <v>57</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="9"/>
+        <v>188.12700000000001</v>
+      </c>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
@@ -3076,38 +3140,40 @@
     </row>
     <row r="23" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H23" s="9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" s="9">
+        <v>2</v>
+      </c>
+      <c r="M23" s="9">
         <v>6</v>
-      </c>
-      <c r="M23" s="9">
-        <v>-6</v>
       </c>
       <c r="N23" s="9"/>
       <c r="O23" s="9">
-        <v>7</v>
-      </c>
-      <c r="P23" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="P23" s="9">
+        <v>5.0880000000000001</v>
+      </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
@@ -3184,61 +3250,64 @@
     </row>
     <row r="24" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:H24" si="8">+C22-C23</f>
+        <f t="shared" ref="C24:H24" si="10">+C22-C23</f>
         <v>0</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-71</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="8"/>
-        <v>-3</v>
+        <f t="shared" si="10"/>
+        <v>-4</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="I24" s="9">
         <f>+I22-I23</f>
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" ref="J24:O24" si="9">+J22-J23</f>
+        <f t="shared" ref="J24:P24" si="11">+J22-J23</f>
         <v>0</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" si="11"/>
+        <v>-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="9"/>
-        <v>18</v>
+        <f t="shared" si="11"/>
+        <v>16</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="9"/>
-        <v>-31</v>
+        <f t="shared" si="11"/>
+        <v>-37</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="9"/>
-        <v>57</v>
-      </c>
-      <c r="P24" s="9"/>
+        <f t="shared" si="11"/>
+        <v>48</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="11"/>
+        <v>183.03900000000002</v>
+      </c>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
@@ -3314,259 +3383,258 @@
       <c r="CK24" s="9"/>
     </row>
     <row r="25" spans="2:89" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9">
-        <v>1</v>
-      </c>
-      <c r="H25" s="9">
-        <v>0</v>
-      </c>
-      <c r="I25" s="9">
-        <v>1</v>
-      </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9">
-        <v>5</v>
-      </c>
-      <c r="L25" s="9">
-        <v>2</v>
-      </c>
-      <c r="M25" s="9">
-        <v>6</v>
-      </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9">
-        <v>9</v>
-      </c>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="9"/>
-      <c r="AD25" s="9"/>
-      <c r="AE25" s="9"/>
-      <c r="AF25" s="9"/>
-      <c r="AG25" s="9"/>
-      <c r="AH25" s="9"/>
-      <c r="AI25" s="9"/>
-      <c r="AJ25" s="9"/>
-      <c r="AK25" s="9"/>
-      <c r="AL25" s="9"/>
-      <c r="AM25" s="9"/>
-      <c r="AN25" s="9"/>
-      <c r="AO25" s="9"/>
-      <c r="AP25" s="9"/>
-      <c r="AQ25" s="9"/>
-      <c r="AR25" s="9"/>
-      <c r="AS25" s="9"/>
-      <c r="AT25" s="9"/>
-      <c r="AU25" s="9"/>
-      <c r="AV25" s="9"/>
-      <c r="AW25" s="9"/>
-      <c r="AX25" s="9"/>
-      <c r="AY25" s="9"/>
-      <c r="AZ25" s="9"/>
-      <c r="BA25" s="9"/>
-      <c r="BB25" s="9"/>
-      <c r="BC25" s="9"/>
-      <c r="BD25" s="9"/>
-      <c r="BE25" s="9"/>
-      <c r="BF25" s="9"/>
-      <c r="BG25" s="9"/>
-      <c r="BH25" s="9"/>
-      <c r="BI25" s="9"/>
-      <c r="BJ25" s="9"/>
-      <c r="BK25" s="9"/>
-      <c r="BL25" s="9"/>
-      <c r="BM25" s="9"/>
-      <c r="BN25" s="9"/>
-      <c r="BO25" s="9"/>
-      <c r="BP25" s="9"/>
-      <c r="BQ25" s="9"/>
-      <c r="BR25" s="9"/>
-      <c r="BS25" s="9"/>
-      <c r="BT25" s="9"/>
-      <c r="BU25" s="9"/>
-      <c r="BV25" s="9"/>
-      <c r="BW25" s="9"/>
-      <c r="BX25" s="9"/>
-      <c r="BY25" s="9"/>
-      <c r="BZ25" s="9"/>
-      <c r="CA25" s="9"/>
-      <c r="CB25" s="9"/>
-      <c r="CC25" s="9"/>
-      <c r="CD25" s="9"/>
-      <c r="CE25" s="9"/>
-      <c r="CF25" s="9"/>
-      <c r="CG25" s="9"/>
-      <c r="CH25" s="9"/>
-      <c r="CI25" s="9"/>
-      <c r="CJ25" s="9"/>
-      <c r="CK25" s="9"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3"/>
+      <c r="AT25" s="3"/>
+      <c r="AU25" s="3"/>
+      <c r="AV25" s="3"/>
+      <c r="AW25" s="3"/>
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="3"/>
+      <c r="AZ25" s="3"/>
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="3"/>
+      <c r="BC25" s="3"/>
+      <c r="BD25" s="3"/>
+      <c r="BE25" s="3"/>
+      <c r="BF25" s="3"/>
+      <c r="BG25" s="3"/>
+      <c r="BH25" s="3"/>
+      <c r="BI25" s="3"/>
+      <c r="BJ25" s="3"/>
+      <c r="BK25" s="3"/>
+      <c r="BL25" s="3"/>
+      <c r="BM25" s="3"/>
+      <c r="BN25" s="3"/>
+      <c r="BO25" s="3"/>
+      <c r="BP25" s="3"/>
+      <c r="BQ25" s="3"/>
+      <c r="BR25" s="3"/>
+      <c r="BS25" s="3"/>
+      <c r="BT25" s="3"/>
+      <c r="BU25" s="3"/>
+      <c r="BV25" s="3"/>
+      <c r="BW25" s="3"/>
+      <c r="BX25" s="3"/>
+      <c r="BY25" s="3"/>
+      <c r="BZ25" s="3"/>
+      <c r="CA25" s="3"/>
+      <c r="CB25" s="3"/>
+      <c r="CC25" s="3"/>
+      <c r="CD25" s="3"/>
+      <c r="CE25" s="3"/>
+      <c r="CF25" s="3"/>
+      <c r="CG25" s="3"/>
+      <c r="CH25" s="3"/>
     </row>
     <row r="26" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="9">
-        <f t="shared" ref="C26:H26" si="10">+C24-C25</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E26" s="9">
-        <f t="shared" si="10"/>
-        <v>-71</v>
-      </c>
-      <c r="F26" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="9">
-        <f t="shared" si="10"/>
-        <v>-4</v>
-      </c>
-      <c r="H26" s="9">
-        <f t="shared" si="10"/>
-        <v>32</v>
-      </c>
-      <c r="I26" s="9">
-        <f>+I24-I25</f>
-        <v>-56</v>
-      </c>
-      <c r="J26" s="9">
-        <f t="shared" ref="J26:O26" si="11">+J24-J25</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="9">
-        <f t="shared" si="11"/>
-        <v>-2</v>
-      </c>
-      <c r="L26" s="9">
-        <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="M26" s="9">
-        <f t="shared" si="11"/>
-        <v>-37</v>
-      </c>
-      <c r="N26" s="9">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="9">
-        <f t="shared" si="11"/>
-        <v>48</v>
-      </c>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="9"/>
-      <c r="AE26" s="9"/>
-      <c r="AF26" s="9"/>
-      <c r="AG26" s="9"/>
-      <c r="AH26" s="9"/>
-      <c r="AI26" s="9"/>
-      <c r="AJ26" s="9"/>
-      <c r="AK26" s="9"/>
-      <c r="AL26" s="9"/>
-      <c r="AM26" s="9"/>
-      <c r="AN26" s="9"/>
-      <c r="AO26" s="9"/>
-      <c r="AP26" s="9"/>
-      <c r="AQ26" s="9"/>
-      <c r="AR26" s="9"/>
-      <c r="AS26" s="9"/>
-      <c r="AT26" s="9"/>
-      <c r="AU26" s="9"/>
-      <c r="AV26" s="9"/>
-      <c r="AW26" s="9"/>
-      <c r="AX26" s="9"/>
-      <c r="AY26" s="9"/>
-      <c r="AZ26" s="9"/>
-      <c r="BA26" s="9"/>
-      <c r="BB26" s="9"/>
-      <c r="BC26" s="9"/>
-      <c r="BD26" s="9"/>
-      <c r="BE26" s="9"/>
-      <c r="BF26" s="9"/>
-      <c r="BG26" s="9"/>
-      <c r="BH26" s="9"/>
-      <c r="BI26" s="9"/>
-      <c r="BJ26" s="9"/>
-      <c r="BK26" s="9"/>
-      <c r="BL26" s="9"/>
-      <c r="BM26" s="9"/>
-      <c r="BN26" s="9"/>
-      <c r="BO26" s="9"/>
-      <c r="BP26" s="9"/>
-      <c r="BQ26" s="9"/>
-      <c r="BR26" s="9"/>
-      <c r="BS26" s="9"/>
-      <c r="BT26" s="9"/>
-      <c r="BU26" s="9"/>
-      <c r="BV26" s="9"/>
-      <c r="BW26" s="9"/>
-      <c r="BX26" s="9"/>
-      <c r="BY26" s="9"/>
-      <c r="BZ26" s="9"/>
-      <c r="CA26" s="9"/>
-      <c r="CB26" s="9"/>
-      <c r="CC26" s="9"/>
-      <c r="CD26" s="9"/>
-      <c r="CE26" s="9"/>
-      <c r="CF26" s="9"/>
-      <c r="CG26" s="9"/>
-      <c r="CH26" s="9"/>
-      <c r="CI26" s="9"/>
-      <c r="CJ26" s="9"/>
-      <c r="CK26" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="C26" s="6" t="e">
+        <f t="shared" ref="C26:D26" si="12">+C24/C27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D26" s="6" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E26" s="6">
+        <f>+E24/E27</f>
+        <v>-0.92207792207792205</v>
+      </c>
+      <c r="F26" s="6" t="e">
+        <f t="shared" ref="F26:P26" si="13">+F24/F27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" si="13"/>
+        <v>-5.128205128205128E-2</v>
+      </c>
+      <c r="H26" s="6">
+        <f t="shared" si="13"/>
+        <v>0.41025641025641024</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="13"/>
+        <v>-0.70886075949367089</v>
+      </c>
+      <c r="J26" s="6" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="6">
+        <f t="shared" si="13"/>
+        <v>-2.5316455696202531E-2</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="13"/>
+        <v>0.2</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="13"/>
+        <v>-0.46250000000000002</v>
+      </c>
+      <c r="N26" s="6" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="6">
+        <f t="shared" si="13"/>
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="P26" s="6">
+        <f t="shared" si="13"/>
+        <v>2.1750998193744655</v>
+      </c>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="3"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="3"/>
+      <c r="AM26" s="3"/>
+      <c r="AN26" s="3"/>
+      <c r="AO26" s="3"/>
+      <c r="AP26" s="3"/>
+      <c r="AQ26" s="3"/>
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="3"/>
+      <c r="AT26" s="3"/>
+      <c r="AU26" s="3"/>
+      <c r="AV26" s="3"/>
+      <c r="AW26" s="3"/>
+      <c r="AX26" s="3"/>
+      <c r="AY26" s="3"/>
+      <c r="AZ26" s="3"/>
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="3"/>
+      <c r="BC26" s="3"/>
+      <c r="BD26" s="3"/>
+      <c r="BE26" s="3"/>
+      <c r="BF26" s="3"/>
+      <c r="BG26" s="3"/>
+      <c r="BH26" s="3"/>
+      <c r="BI26" s="3"/>
+      <c r="BJ26" s="3"/>
+      <c r="BK26" s="3"/>
+      <c r="BL26" s="3"/>
+      <c r="BM26" s="3"/>
+      <c r="BN26" s="3"/>
+      <c r="BO26" s="3"/>
+      <c r="BP26" s="3"/>
+      <c r="BQ26" s="3"/>
+      <c r="BR26" s="3"/>
+      <c r="BS26" s="3"/>
+      <c r="BT26" s="3"/>
+      <c r="BU26" s="3"/>
+      <c r="BV26" s="3"/>
+      <c r="BW26" s="3"/>
+      <c r="BX26" s="3"/>
+      <c r="BY26" s="3"/>
+      <c r="BZ26" s="3"/>
+      <c r="CA26" s="3"/>
+      <c r="CB26" s="3"/>
+      <c r="CC26" s="3"/>
+      <c r="CD26" s="3"/>
+      <c r="CE26" s="3"/>
+      <c r="CF26" s="3"/>
+      <c r="CG26" s="3"/>
+      <c r="CH26" s="3"/>
     </row>
     <row r="27" spans="2:89" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3">
+        <v>77</v>
+      </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="G27" s="3">
+        <v>78</v>
+      </c>
+      <c r="H27" s="3">
+        <v>78</v>
+      </c>
+      <c r="I27" s="3">
+        <v>79</v>
+      </c>
       <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
+      <c r="K27" s="3">
+        <v>79</v>
+      </c>
+      <c r="L27" s="3">
+        <v>80</v>
+      </c>
+      <c r="M27" s="3">
+        <v>80</v>
+      </c>
       <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
+      <c r="O27" s="3">
+        <v>81</v>
+      </c>
+      <c r="P27" s="3">
+        <v>84.152000000000001</v>
+      </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
@@ -3639,61 +3707,19 @@
       <c r="CH27" s="3"/>
     </row>
     <row r="28" spans="2:89" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="6" t="e">
-        <f t="shared" ref="C28:D28" si="12">+C26/C29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D28" s="6" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E28" s="6">
-        <f>+E26/E29</f>
-        <v>-0.92207792207792205</v>
-      </c>
-      <c r="F28" s="6" t="e">
-        <f t="shared" ref="F28:O28" si="13">+F26/F29</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G28" s="6">
-        <f t="shared" si="13"/>
-        <v>-5.128205128205128E-2</v>
-      </c>
-      <c r="H28" s="6">
-        <f t="shared" si="13"/>
-        <v>0.41025641025641024</v>
-      </c>
-      <c r="I28" s="6">
-        <f t="shared" si="13"/>
-        <v>-0.70886075949367089</v>
-      </c>
-      <c r="J28" s="6" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K28" s="6">
-        <f t="shared" si="13"/>
-        <v>-2.5316455696202531E-2</v>
-      </c>
-      <c r="L28" s="6">
-        <f t="shared" si="13"/>
-        <v>0.2</v>
-      </c>
-      <c r="M28" s="6">
-        <f t="shared" si="13"/>
-        <v>-0.46250000000000002</v>
-      </c>
-      <c r="N28" s="6" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="6">
-        <f t="shared" si="13"/>
-        <v>0.59259259259259256</v>
-      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -3768,39 +3794,56 @@
     </row>
     <row r="29" spans="2:89" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="3">
-        <v>77</v>
-      </c>
+      <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3">
-        <v>78</v>
-      </c>
-      <c r="H29" s="3">
-        <v>78</v>
-      </c>
-      <c r="I29" s="3">
-        <v>79</v>
-      </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3">
-        <v>79</v>
-      </c>
-      <c r="L29" s="3">
-        <v>80</v>
-      </c>
-      <c r="M29" s="3">
-        <v>80</v>
-      </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3">
-        <v>81</v>
-      </c>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
+      <c r="G29" s="7" t="e">
+        <f t="shared" ref="G29:H29" si="14">+G8/C8-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H29" s="7" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I29" s="7">
+        <f>+I8/E8-1</f>
+        <v>8.8365243004417948E-3</v>
+      </c>
+      <c r="J29" s="7" t="e">
+        <f t="shared" ref="J29:N29" si="15">+J8/F8-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="15"/>
+        <v>2.1849963583393528E-3</v>
+      </c>
+      <c r="M29" s="7">
+        <f t="shared" si="15"/>
+        <v>1.2408759124087565E-2</v>
+      </c>
+      <c r="N29" s="7" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O29" s="7">
+        <f t="shared" ref="O29" si="16">+O8/K8-1</f>
+        <v>3.2656023222060959E-2</v>
+      </c>
+      <c r="P29" s="7">
+        <f t="shared" ref="P29" si="17">+P8/L8-1</f>
+        <v>3.9244186046511587E-2</v>
+      </c>
+      <c r="Q29" s="7">
+        <f t="shared" ref="Q29" si="18">+Q8/M8-1</f>
+        <v>-1</v>
+      </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3872,21 +3915,57 @@
       <c r="CH29" s="3"/>
     </row>
     <row r="30" spans="2:89" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
+      <c r="G30" s="7" t="e">
+        <f t="shared" ref="G30:H33" si="19">+G10/C10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H30" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I30" s="7">
+        <f>+I10/E10-1</f>
+        <v>2.0746887966804906E-2</v>
+      </c>
+      <c r="J30" s="7" t="e">
+        <f t="shared" ref="J30:N33" si="20">+J10/F10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" s="7">
+        <f t="shared" si="20"/>
+        <v>-1.0973936899862813E-2</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="20"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="20"/>
+        <v>5.4200542005420127E-2</v>
+      </c>
+      <c r="N30" s="7" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O30" s="7">
+        <f t="shared" ref="O30:O33" si="21">+O10/K10-1</f>
+        <v>0.1137309292649098</v>
+      </c>
+      <c r="P30" s="7">
+        <f t="shared" ref="P30:P33" si="22">+P10/L10-1</f>
+        <v>8.8363636363636422E-2</v>
+      </c>
+      <c r="Q30" s="7">
+        <f t="shared" ref="Q30:Q33" si="23">+Q10/M10-1</f>
+        <v>-1</v>
+      </c>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -3966,47 +4045,47 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="7" t="e">
-        <f t="shared" ref="G31:H31" si="14">+G10/C10-1</f>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="7">
-        <f>+I10/E10-1</f>
-        <v>8.8365243004417948E-3</v>
+        <f t="shared" ref="I31:I33" si="24">+I11/E11-1</f>
+        <v>7.5916230366492199E-2</v>
       </c>
       <c r="J31" s="7" t="e">
-        <f t="shared" ref="J31:N31" si="15">+J10/F10-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>-3.563474387527843E-2</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" si="15"/>
-        <v>2.1849963583393528E-3</v>
+        <f t="shared" si="20"/>
+        <v>-5.5813953488372148E-2</v>
       </c>
       <c r="M31" s="7">
-        <f t="shared" si="15"/>
-        <v>1.2408759124087565E-2</v>
+        <f t="shared" si="20"/>
+        <v>4.3795620437956151E-2</v>
       </c>
       <c r="N31" s="7" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O31" s="7">
-        <f t="shared" ref="O31" si="16">+O10/K10-1</f>
-        <v>3.2656023222060959E-2</v>
+        <f t="shared" si="21"/>
+        <v>8.3140877598152363E-2</v>
       </c>
       <c r="P31" s="7">
-        <f t="shared" ref="P31" si="17">+P10/L10-1</f>
-        <v>-1</v>
+        <f t="shared" si="22"/>
+        <v>8.226600985221677E-2</v>
       </c>
       <c r="Q31" s="7">
-        <f t="shared" ref="Q31" si="18">+Q10/M10-1</f>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="R31" s="3"/>
@@ -4088,7 +4167,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="7" t="e">
-        <f t="shared" ref="G32:H35" si="19">+G12/C12-1</f>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H32" s="7" t="e">
@@ -4096,39 +4175,39 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="7">
-        <f>+I12/E12-1</f>
-        <v>2.0746887966804906E-2</v>
+        <f t="shared" si="24"/>
+        <v>0.23750000000000004</v>
       </c>
       <c r="J32" s="7" t="e">
-        <f t="shared" ref="J32:N35" si="20">+J12/F12-1</f>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K32" s="7">
         <f t="shared" si="20"/>
-        <v>-1.0973936899862813E-2</v>
+        <v>9.9447513812154664E-2</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="20"/>
-        <v>3.125E-2</v>
+        <v>0.21925133689839571</v>
       </c>
       <c r="M32" s="7">
         <f t="shared" si="20"/>
-        <v>5.4200542005420127E-2</v>
+        <v>0.33838383838383845</v>
       </c>
       <c r="N32" s="7" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O32" s="7">
-        <f t="shared" ref="O32:O35" si="21">+O12/K12-1</f>
-        <v>0.1137309292649098</v>
+        <f t="shared" si="21"/>
+        <v>0.44723618090452266</v>
       </c>
       <c r="P32" s="7">
-        <f t="shared" ref="P32:P35" si="22">+P12/L12-1</f>
-        <v>-1</v>
+        <f t="shared" si="22"/>
+        <v>0.1991228070175437</v>
       </c>
       <c r="Q32" s="7">
-        <f t="shared" ref="Q32:Q35" si="23">+Q12/M12-1</f>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="R32" s="3"/>
@@ -4202,54 +4281,54 @@
       <c r="CH32" s="3"/>
     </row>
     <row r="33" spans="2:86" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="7" t="e">
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="12" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="7" t="e">
+      <c r="H33" s="12" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I33" s="7">
-        <f t="shared" ref="I33:I35" si="24">+I13/E13-1</f>
-        <v>7.5916230366492199E-2</v>
-      </c>
-      <c r="J33" s="7" t="e">
+      <c r="I33" s="12">
+        <f t="shared" si="24"/>
+        <v>6.4822134387351849E-2</v>
+      </c>
+      <c r="J33" s="12" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="12">
         <f t="shared" si="20"/>
-        <v>-3.563474387527843E-2</v>
-      </c>
-      <c r="L33" s="7">
+        <v>-4.4150110375276164E-3</v>
+      </c>
+      <c r="L33" s="12">
         <f t="shared" si="20"/>
-        <v>-5.5813953488372148E-2</v>
-      </c>
-      <c r="M33" s="7">
+        <v>2.9640084685956136E-2</v>
+      </c>
+      <c r="M33" s="12">
         <f t="shared" si="20"/>
-        <v>4.3795620437956151E-2</v>
-      </c>
-      <c r="N33" s="7" t="e">
+        <v>9.2798812175204137E-2</v>
+      </c>
+      <c r="N33" s="12" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O33" s="7">
+      <c r="O33" s="12">
         <f t="shared" si="21"/>
-        <v>8.3140877598152363E-2</v>
-      </c>
-      <c r="P33" s="7">
+        <v>0.15299334811529941</v>
+      </c>
+      <c r="P33" s="12">
         <f t="shared" si="22"/>
-        <v>-1</v>
-      </c>
-      <c r="Q33" s="7">
+        <v>0.10397738176833449</v>
+      </c>
+      <c r="Q33" s="12">
         <f t="shared" si="23"/>
         <v>-1</v>
       </c>
@@ -4327,53 +4406,65 @@
       <c r="B34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="7" t="e">
-        <f t="shared" si="19"/>
+      <c r="C34" s="7" t="e">
+        <f t="shared" ref="C34:L34" si="25">+C15/C13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="7" t="e">
-        <f t="shared" si="19"/>
+      <c r="D34" s="7" t="e">
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="E34" s="7">
+        <f t="shared" si="25"/>
+        <v>0.3375494071146245</v>
+      </c>
+      <c r="F34" s="7" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G34" s="7">
+        <f t="shared" si="25"/>
+        <v>0.36865342163355408</v>
+      </c>
+      <c r="H34" s="7">
+        <f t="shared" si="25"/>
+        <v>0.35356386732533523</v>
+      </c>
       <c r="I34" s="7">
-        <f t="shared" si="24"/>
-        <v>0.23750000000000004</v>
+        <f t="shared" si="25"/>
+        <v>0.34743875278396436</v>
       </c>
       <c r="J34" s="7" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="7">
-        <f t="shared" si="20"/>
-        <v>9.9447513812154664E-2</v>
+        <f t="shared" si="25"/>
+        <v>0.35033259423503327</v>
       </c>
       <c r="L34" s="7">
-        <f t="shared" si="20"/>
-        <v>0.21925133689839571</v>
+        <f t="shared" si="25"/>
+        <v>0.3557230980123372</v>
       </c>
       <c r="M34" s="7">
-        <f t="shared" si="20"/>
-        <v>0.33838383838383845</v>
+        <f>+M15/M13</f>
+        <v>0.3641304347826087</v>
       </c>
       <c r="N34" s="7" t="e">
-        <f t="shared" si="20"/>
+        <f>+N15/N13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O34" s="7">
-        <f t="shared" si="21"/>
-        <v>0.44723618090452266</v>
+        <f t="shared" ref="O34:Q34" si="26">+O15/O13</f>
+        <v>0.375</v>
       </c>
       <c r="P34" s="7">
-        <f t="shared" si="22"/>
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="7">
-        <f t="shared" si="23"/>
-        <v>-1</v>
+        <f t="shared" si="26"/>
+        <v>0.47139913441522119</v>
+      </c>
+      <c r="Q34" s="7" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
@@ -4446,56 +4537,68 @@
       <c r="CH34" s="3"/>
     </row>
     <row r="35" spans="2:86" x14ac:dyDescent="0.2">
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12" t="e">
-        <f t="shared" si="19"/>
+      <c r="C35" s="13" t="e">
+        <f t="shared" ref="C35:L35" si="27">+C17/C13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="12" t="e">
-        <f t="shared" si="19"/>
+      <c r="D35" s="13" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I35" s="12">
-        <f t="shared" si="24"/>
-        <v>6.4822134387351849E-2</v>
-      </c>
-      <c r="J35" s="12" t="e">
-        <f t="shared" si="20"/>
+      <c r="E35" s="13">
+        <f t="shared" si="27"/>
+        <v>-5.2964426877470355E-2</v>
+      </c>
+      <c r="F35" s="13" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K35" s="12">
-        <f t="shared" si="20"/>
-        <v>-4.4150110375276164E-3</v>
-      </c>
-      <c r="L35" s="12">
-        <f t="shared" si="20"/>
-        <v>2.9640084685956136E-2</v>
-      </c>
-      <c r="M35" s="12">
-        <f t="shared" si="20"/>
-        <v>9.2798812175204137E-2</v>
-      </c>
-      <c r="N35" s="12" t="e">
-        <f t="shared" si="20"/>
+      <c r="G35" s="13">
+        <f t="shared" si="27"/>
+        <v>1.9131714495952908E-2</v>
+      </c>
+      <c r="H35" s="13">
+        <f t="shared" si="27"/>
+        <v>4.3754410726887794E-2</v>
+      </c>
+      <c r="I35" s="13">
+        <f t="shared" si="27"/>
+        <v>-3.4892353377876766E-2</v>
+      </c>
+      <c r="J35" s="13" t="e">
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O35" s="12">
-        <f t="shared" si="21"/>
-        <v>0.15299334811529941</v>
-      </c>
-      <c r="P35" s="12">
-        <f t="shared" si="22"/>
-        <v>-1</v>
-      </c>
-      <c r="Q35" s="12">
-        <f t="shared" si="23"/>
-        <v>-1</v>
+      <c r="K35" s="13">
+        <f t="shared" si="27"/>
+        <v>1.4781966001478197E-2</v>
+      </c>
+      <c r="L35" s="13">
+        <f t="shared" si="27"/>
+        <v>2.8101439342015078E-2</v>
+      </c>
+      <c r="M35" s="13">
+        <f>+M17/M13</f>
+        <v>-1.2907608695652174E-2</v>
+      </c>
+      <c r="N35" s="13" t="e">
+        <f>+N17/N13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O35" s="13">
+        <f t="shared" ref="O35:Q35" si="28">+O17/O13</f>
+        <v>4.8717948717948718E-2</v>
+      </c>
+      <c r="P35" s="13">
+        <f t="shared" si="28"/>
+        <v>0.15932794562374317</v>
+      </c>
+      <c r="Q35" s="13" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
@@ -4572,63 +4675,63 @@
         <v>48</v>
       </c>
       <c r="C36" s="7" t="e">
-        <f t="shared" ref="C36:L36" si="25">+C17/C15</f>
+        <f t="shared" ref="C36:L36" si="29">+C23/C22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D36" s="7" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E36" s="7">
-        <f t="shared" si="25"/>
-        <v>0.3375494071146245</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="F36" s="7" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G36" s="7">
-        <f t="shared" si="25"/>
-        <v>0.36865342163355408</v>
+        <f t="shared" si="29"/>
+        <v>-0.33333333333333331</v>
       </c>
       <c r="H36" s="7">
-        <f t="shared" si="25"/>
-        <v>0.35356386732533523</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="I36" s="7">
-        <f t="shared" si="25"/>
-        <v>0.34743875278396436</v>
+        <f t="shared" si="29"/>
+        <v>-1.8181818181818181E-2</v>
       </c>
       <c r="J36" s="7" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="7">
-        <f t="shared" si="25"/>
-        <v>0.35033259423503327</v>
+        <f t="shared" si="29"/>
+        <v>1.6666666666666667</v>
       </c>
       <c r="L36" s="7">
-        <f t="shared" si="25"/>
-        <v>0.3557230980123372</v>
+        <f t="shared" si="29"/>
+        <v>0.1111111111111111</v>
       </c>
       <c r="M36" s="7">
-        <f>+M17/M15</f>
-        <v>0.3641304347826087</v>
+        <f>+M23/M22</f>
+        <v>-0.19354838709677419</v>
       </c>
       <c r="N36" s="7" t="e">
-        <f>+N17/N15</f>
+        <f>+N23/N22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O36" s="7">
-        <f t="shared" ref="O36:Q36" si="26">+O17/O15</f>
-        <v>0.375</v>
-      </c>
-      <c r="P36" s="7" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
+        <f t="shared" ref="O36:Q36" si="30">+O23/O22</f>
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="P36" s="7">
+        <f t="shared" si="30"/>
+        <v>2.7045559648535299E-2</v>
       </c>
       <c r="Q36" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R36" s="3"/>
@@ -4702,69 +4805,21 @@
       <c r="CH36" s="3"/>
     </row>
     <row r="37" spans="2:86" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="13" t="e">
-        <f t="shared" ref="C37:L37" si="27">+C19/C15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D37" s="13" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E37" s="13">
-        <f t="shared" si="27"/>
-        <v>-5.2964426877470355E-2</v>
-      </c>
-      <c r="F37" s="13" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G37" s="13">
-        <f t="shared" si="27"/>
-        <v>1.9131714495952908E-2</v>
-      </c>
-      <c r="H37" s="13">
-        <f t="shared" si="27"/>
-        <v>4.3754410726887794E-2</v>
-      </c>
-      <c r="I37" s="13">
-        <f t="shared" si="27"/>
-        <v>-3.4892353377876766E-2</v>
-      </c>
-      <c r="J37" s="13" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K37" s="13">
-        <f t="shared" si="27"/>
-        <v>1.4781966001478197E-2</v>
-      </c>
-      <c r="L37" s="13">
-        <f t="shared" si="27"/>
-        <v>2.8101439342015078E-2</v>
-      </c>
-      <c r="M37" s="13">
-        <f>+M19/M15</f>
-        <v>-1.2907608695652174E-2</v>
-      </c>
-      <c r="N37" s="13" t="e">
-        <f>+N19/N15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O37" s="13">
-        <f t="shared" ref="O37:Q37" si="28">+O19/O15</f>
-        <v>4.8717948717948718E-2</v>
-      </c>
-      <c r="P37" s="13" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q37" s="13" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
@@ -4836,69 +4891,21 @@
       <c r="CH37" s="3"/>
     </row>
     <row r="38" spans="2:86" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="7" t="e">
-        <f t="shared" ref="C38:L38" si="29">+C25/C24</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D38" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E38" s="7">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G38" s="7">
-        <f t="shared" si="29"/>
-        <v>-0.33333333333333331</v>
-      </c>
-      <c r="H38" s="7">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="7">
-        <f t="shared" si="29"/>
-        <v>-1.8181818181818181E-2</v>
-      </c>
-      <c r="J38" s="7" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K38" s="7">
-        <f t="shared" si="29"/>
-        <v>1.6666666666666667</v>
-      </c>
-      <c r="L38" s="7">
-        <f t="shared" si="29"/>
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="M38" s="7">
-        <f>+M25/M24</f>
-        <v>-0.19354838709677419</v>
-      </c>
-      <c r="N38" s="7" t="e">
-        <f>+N25/N24</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O38" s="7">
-        <f t="shared" ref="O38:Q38" si="30">+O25/O24</f>
-        <v>0.15789473684210525</v>
-      </c>
-      <c r="P38" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q38" s="7" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
@@ -37563,178 +37570,6 @@
       <c r="CG417" s="3"/>
       <c r="CH417" s="3"/>
     </row>
-    <row r="418" spans="3:86" x14ac:dyDescent="0.2">
-      <c r="C418" s="3"/>
-      <c r="D418" s="3"/>
-      <c r="E418" s="3"/>
-      <c r="F418" s="3"/>
-      <c r="G418" s="3"/>
-      <c r="H418" s="3"/>
-      <c r="I418" s="3"/>
-      <c r="J418" s="3"/>
-      <c r="K418" s="3"/>
-      <c r="L418" s="3"/>
-      <c r="M418" s="3"/>
-      <c r="N418" s="3"/>
-      <c r="O418" s="3"/>
-      <c r="P418" s="3"/>
-      <c r="Q418" s="3"/>
-      <c r="R418" s="3"/>
-      <c r="S418" s="3"/>
-      <c r="T418" s="3"/>
-      <c r="U418" s="3"/>
-      <c r="V418" s="3"/>
-      <c r="W418" s="3"/>
-      <c r="X418" s="3"/>
-      <c r="Y418" s="3"/>
-      <c r="Z418" s="3"/>
-      <c r="AA418" s="3"/>
-      <c r="AB418" s="3"/>
-      <c r="AC418" s="3"/>
-      <c r="AD418" s="3"/>
-      <c r="AE418" s="3"/>
-      <c r="AF418" s="3"/>
-      <c r="AG418" s="3"/>
-      <c r="AH418" s="3"/>
-      <c r="AI418" s="3"/>
-      <c r="AJ418" s="3"/>
-      <c r="AK418" s="3"/>
-      <c r="AL418" s="3"/>
-      <c r="AM418" s="3"/>
-      <c r="AN418" s="3"/>
-      <c r="AO418" s="3"/>
-      <c r="AP418" s="3"/>
-      <c r="AQ418" s="3"/>
-      <c r="AR418" s="3"/>
-      <c r="AS418" s="3"/>
-      <c r="AT418" s="3"/>
-      <c r="AU418" s="3"/>
-      <c r="AV418" s="3"/>
-      <c r="AW418" s="3"/>
-      <c r="AX418" s="3"/>
-      <c r="AY418" s="3"/>
-      <c r="AZ418" s="3"/>
-      <c r="BA418" s="3"/>
-      <c r="BB418" s="3"/>
-      <c r="BC418" s="3"/>
-      <c r="BD418" s="3"/>
-      <c r="BE418" s="3"/>
-      <c r="BF418" s="3"/>
-      <c r="BG418" s="3"/>
-      <c r="BH418" s="3"/>
-      <c r="BI418" s="3"/>
-      <c r="BJ418" s="3"/>
-      <c r="BK418" s="3"/>
-      <c r="BL418" s="3"/>
-      <c r="BM418" s="3"/>
-      <c r="BN418" s="3"/>
-      <c r="BO418" s="3"/>
-      <c r="BP418" s="3"/>
-      <c r="BQ418" s="3"/>
-      <c r="BR418" s="3"/>
-      <c r="BS418" s="3"/>
-      <c r="BT418" s="3"/>
-      <c r="BU418" s="3"/>
-      <c r="BV418" s="3"/>
-      <c r="BW418" s="3"/>
-      <c r="BX418" s="3"/>
-      <c r="BY418" s="3"/>
-      <c r="BZ418" s="3"/>
-      <c r="CA418" s="3"/>
-      <c r="CB418" s="3"/>
-      <c r="CC418" s="3"/>
-      <c r="CD418" s="3"/>
-      <c r="CE418" s="3"/>
-      <c r="CF418" s="3"/>
-      <c r="CG418" s="3"/>
-      <c r="CH418" s="3"/>
-    </row>
-    <row r="419" spans="3:86" x14ac:dyDescent="0.2">
-      <c r="C419" s="3"/>
-      <c r="D419" s="3"/>
-      <c r="E419" s="3"/>
-      <c r="F419" s="3"/>
-      <c r="G419" s="3"/>
-      <c r="H419" s="3"/>
-      <c r="I419" s="3"/>
-      <c r="J419" s="3"/>
-      <c r="K419" s="3"/>
-      <c r="L419" s="3"/>
-      <c r="M419" s="3"/>
-      <c r="N419" s="3"/>
-      <c r="O419" s="3"/>
-      <c r="P419" s="3"/>
-      <c r="Q419" s="3"/>
-      <c r="R419" s="3"/>
-      <c r="S419" s="3"/>
-      <c r="T419" s="3"/>
-      <c r="U419" s="3"/>
-      <c r="V419" s="3"/>
-      <c r="W419" s="3"/>
-      <c r="X419" s="3"/>
-      <c r="Y419" s="3"/>
-      <c r="Z419" s="3"/>
-      <c r="AA419" s="3"/>
-      <c r="AB419" s="3"/>
-      <c r="AC419" s="3"/>
-      <c r="AD419" s="3"/>
-      <c r="AE419" s="3"/>
-      <c r="AF419" s="3"/>
-      <c r="AG419" s="3"/>
-      <c r="AH419" s="3"/>
-      <c r="AI419" s="3"/>
-      <c r="AJ419" s="3"/>
-      <c r="AK419" s="3"/>
-      <c r="AL419" s="3"/>
-      <c r="AM419" s="3"/>
-      <c r="AN419" s="3"/>
-      <c r="AO419" s="3"/>
-      <c r="AP419" s="3"/>
-      <c r="AQ419" s="3"/>
-      <c r="AR419" s="3"/>
-      <c r="AS419" s="3"/>
-      <c r="AT419" s="3"/>
-      <c r="AU419" s="3"/>
-      <c r="AV419" s="3"/>
-      <c r="AW419" s="3"/>
-      <c r="AX419" s="3"/>
-      <c r="AY419" s="3"/>
-      <c r="AZ419" s="3"/>
-      <c r="BA419" s="3"/>
-      <c r="BB419" s="3"/>
-      <c r="BC419" s="3"/>
-      <c r="BD419" s="3"/>
-      <c r="BE419" s="3"/>
-      <c r="BF419" s="3"/>
-      <c r="BG419" s="3"/>
-      <c r="BH419" s="3"/>
-      <c r="BI419" s="3"/>
-      <c r="BJ419" s="3"/>
-      <c r="BK419" s="3"/>
-      <c r="BL419" s="3"/>
-      <c r="BM419" s="3"/>
-      <c r="BN419" s="3"/>
-      <c r="BO419" s="3"/>
-      <c r="BP419" s="3"/>
-      <c r="BQ419" s="3"/>
-      <c r="BR419" s="3"/>
-      <c r="BS419" s="3"/>
-      <c r="BT419" s="3"/>
-      <c r="BU419" s="3"/>
-      <c r="BV419" s="3"/>
-      <c r="BW419" s="3"/>
-      <c r="BX419" s="3"/>
-      <c r="BY419" s="3"/>
-      <c r="BZ419" s="3"/>
-      <c r="CA419" s="3"/>
-      <c r="CB419" s="3"/>
-      <c r="CC419" s="3"/>
-      <c r="CD419" s="3"/>
-      <c r="CE419" s="3"/>
-      <c r="CF419" s="3"/>
-      <c r="CG419" s="3"/>
-      <c r="CH419" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{8F02A12F-F5DD-4F1E-A486-2A56BC548541}"/>
